--- a/STC/STC- Testcase document.xlsx
+++ b/STC/STC- Testcase document.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Testcase Document\STC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755A8A2C-78CC-44BA-820F-D41D86E5053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5399A6A-5DC2-424B-AD5B-2CB6DBE6EA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2509,28 +2509,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3174,11 +3174,11 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="43" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
@@ -3568,10 +3568,10 @@
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="B31" s="13"/>
+      <c r="B31" s="15"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
@@ -3893,10 +3893,10 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="53" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="18" t="s">
         <v>768</v>
       </c>
-      <c r="B44" s="12"/>
+      <c r="B44" s="18"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
@@ -4334,10 +4334,10 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B62" s="11"/>
+      <c r="B62" s="13"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
@@ -4688,10 +4688,10 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B76" s="11"/>
+      <c r="B76" s="13"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
@@ -5245,10 +5245,10 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="13" t="s">
         <v>714</v>
       </c>
-      <c r="B97" s="11"/>
+      <c r="B97" s="13"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
@@ -5570,10 +5570,10 @@
       </c>
     </row>
     <row r="110" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="14" t="s">
         <v>740</v>
       </c>
-      <c r="B110" s="16"/>
+      <c r="B110" s="14"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
@@ -5871,8 +5871,8 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="17"/>
-      <c r="B123" s="18"/>
+      <c r="A123" s="16"/>
+      <c r="B123" s="17"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -6212,10 +6212,10 @@
       <c r="I135" s="2"/>
     </row>
     <row r="136" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="B136" s="15"/>
+      <c r="B136" s="12"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -6631,11 +6631,11 @@
       </c>
     </row>
     <row r="152" spans="1:9" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="B152" s="13"/>
-      <c r="C152" s="15"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="12"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -7224,11 +7224,11 @@
       </c>
     </row>
     <row r="174" spans="1:9" ht="41" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="11" t="s">
         <v>770</v>
       </c>
-      <c r="B174" s="13"/>
-      <c r="C174" s="15"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="12"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
@@ -7904,11 +7904,11 @@
       </c>
     </row>
     <row r="199" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="B199" s="13"/>
-      <c r="C199" s="15"/>
+      <c r="B199" s="15"/>
+      <c r="C199" s="12"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
@@ -8732,10 +8732,10 @@
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="1:9" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="14" t="s">
+      <c r="A229" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="B229" s="15"/>
+      <c r="B229" s="12"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -9470,10 +9470,10 @@
       </c>
     </row>
     <row r="256" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="14" t="s">
+      <c r="A256" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="B256" s="15"/>
+      <c r="B256" s="12"/>
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -10093,6 +10093,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A256:B256"/>
     <mergeCell ref="A97:B97"/>
     <mergeCell ref="A110:B110"/>
@@ -10102,11 +10107,6 @@
     <mergeCell ref="A136:B136"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
